--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/button_style_pref.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/global/button_style_pref.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="C2" t="n">
-        <v>41.5</v>
+        <v>41.07</v>
       </c>
     </row>
     <row r="3">
@@ -465,36 +465,36 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C3" t="n">
-        <v>26.5</v>
+        <v>27.68</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Raised / Shadowed (Button with shadow or depth effect)</t>
+          <t>Sharp Square (Clean, professional 90-degree corners)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
-        <v>10.5</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Sharp Square (Clean, professional 90-degree corners)</t>
+          <t>Raised / Shadowed (Button with shadow or depth effect)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="7">
@@ -520,7 +520,7 @@
         <v>7</v>
       </c>
       <c r="C7" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>
